--- a/output/ARKK/00_Starter_Residual_over_7.5pct/ARKK_starter_residual_analysis.xlsx
+++ b/output/ARKK/00_Starter_Residual_over_7.5pct/ARKK_starter_residual_analysis.xlsx
@@ -555,10 +555,10 @@
         <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="O2" t="n">
-        <v>510.2027027027027</v>
+        <v>558.28</v>
       </c>
     </row>
   </sheetData>
@@ -572,52 +572,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Bloomberg Name</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Entry Date</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Entry Weight %</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Max Weight Achieved %</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Final Weight %</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Outcome</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Days to Outcome</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Days as Small Position</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -628,57 +585,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Bloomberg Name</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Transition Date</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Peak Weight Before %</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Weight at Transition %</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Weight Drawdown %</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Max Weight After %</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Final Weight %</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Outcome</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Days as Residual</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -689,7 +598,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E75"/>
+  <dimension ref="A1:E76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1045,381 +954,381 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>BIDU US Equity</t>
+          <t>BABA US Equity</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
-        <v>43690</v>
+        <v>43363</v>
       </c>
       <c r="C19" s="2" t="n">
-        <v>44176</v>
+        <v>45925</v>
       </c>
       <c r="D19" t="n">
-        <v>486</v>
+        <v>2562</v>
       </c>
       <c r="E19" t="n">
-        <v>0.1774855932996128</v>
+        <v>0.1555838802032586</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>CRSP US Equity</t>
+          <t>BIDU US Equity</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>43220</v>
+        <v>43690</v>
       </c>
       <c r="C20" s="2" t="n">
-        <v>43252</v>
+        <v>44176</v>
       </c>
       <c r="D20" t="n">
-        <v>32</v>
+        <v>486</v>
       </c>
       <c r="E20" t="n">
-        <v>0.2671023170990939</v>
+        <v>0.1774855932996128</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>DDD US Equity</t>
+          <t>BIDU US Equity</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
-        <v>42794</v>
+        <v>44334</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>44512</v>
+        <v>45925</v>
       </c>
       <c r="D21" t="n">
-        <v>1718</v>
+        <v>1591</v>
       </c>
       <c r="E21" t="n">
-        <v>0.2516488494639003</v>
+        <v>0.1536917164820487</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>EXAS US Equity</t>
+          <t>CRSP US Equity</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
-        <v>45475</v>
+        <v>43220</v>
       </c>
       <c r="C22" s="2" t="n">
-        <v>45877</v>
+        <v>43252</v>
       </c>
       <c r="D22" t="n">
-        <v>402</v>
+        <v>32</v>
       </c>
       <c r="E22" t="n">
-        <v>0.8467072203452185</v>
+        <v>0.2671023170990939</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>FANUY US Equity</t>
+          <t>DDD US Equity</t>
         </is>
       </c>
       <c r="B23" s="2" t="n">
-        <v>42398</v>
+        <v>42794</v>
       </c>
       <c r="C23" s="2" t="n">
-        <v>42948</v>
+        <v>44512</v>
       </c>
       <c r="D23" t="n">
-        <v>550</v>
+        <v>1718</v>
       </c>
       <c r="E23" t="n">
-        <v>0.4875444081657636</v>
+        <v>0.2516488494639003</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>GM US Equity</t>
+          <t>EXAS US Equity</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
-        <v>42829</v>
+        <v>45475</v>
       </c>
       <c r="C24" s="2" t="n">
-        <v>43033</v>
+        <v>45877</v>
       </c>
       <c r="D24" t="n">
-        <v>204</v>
+        <v>402</v>
       </c>
       <c r="E24" t="n">
-        <v>0.4913143939062111</v>
+        <v>0.8467072203452185</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>GOOG US Equity</t>
+          <t>FANUY US Equity</t>
         </is>
       </c>
       <c r="B25" s="2" t="n">
-        <v>42142</v>
+        <v>42398</v>
       </c>
       <c r="C25" s="2" t="n">
-        <v>42458</v>
+        <v>42948</v>
       </c>
       <c r="D25" t="n">
-        <v>316</v>
+        <v>550</v>
       </c>
       <c r="E25" t="n">
-        <v>1.968287853227933</v>
+        <v>0.4875444081657636</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ICE US Equity</t>
+          <t>GM US Equity</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
-        <v>43427</v>
+        <v>42829</v>
       </c>
       <c r="C26" s="2" t="n">
-        <v>44062</v>
+        <v>43033</v>
       </c>
       <c r="D26" t="n">
-        <v>635</v>
+        <v>204</v>
       </c>
       <c r="E26" t="n">
-        <v>0.4197300085576299</v>
+        <v>0.4913143939062111</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>ILMN US Equity</t>
+          <t>GOOG US Equity</t>
         </is>
       </c>
       <c r="B27" s="2" t="n">
-        <v>44140</v>
+        <v>42142</v>
       </c>
       <c r="C27" s="2" t="n">
-        <v>45600</v>
+        <v>42458</v>
       </c>
       <c r="D27" t="n">
-        <v>1460</v>
+        <v>316</v>
       </c>
       <c r="E27" t="n">
-        <v>0.1631762599743918</v>
+        <v>1.968287853227933</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>INTU US Equity</t>
+          <t>ICE US Equity</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
-        <v>42199</v>
+        <v>43427</v>
       </c>
       <c r="C28" s="2" t="n">
-        <v>42915</v>
+        <v>44062</v>
       </c>
       <c r="D28" t="n">
-        <v>716</v>
+        <v>635</v>
       </c>
       <c r="E28" t="n">
-        <v>0.4960517874846671</v>
+        <v>0.4197300085576299</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>IOVA US Equity</t>
+          <t>ILMN US Equity</t>
         </is>
       </c>
       <c r="B29" s="2" t="n">
-        <v>43909</v>
+        <v>44140</v>
       </c>
       <c r="C29" s="2" t="n">
-        <v>43983</v>
+        <v>45600</v>
       </c>
       <c r="D29" t="n">
-        <v>74</v>
+        <v>1460</v>
       </c>
       <c r="E29" t="n">
-        <v>0.4817989418673881</v>
+        <v>0.1631762599743918</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>IRDM US Equity</t>
+          <t>INTU US Equity</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
-        <v>44610</v>
+        <v>42199</v>
       </c>
       <c r="C30" s="2" t="n">
-        <v>45700</v>
+        <v>42915</v>
       </c>
       <c r="D30" t="n">
-        <v>1090</v>
+        <v>716</v>
       </c>
       <c r="E30" t="n">
-        <v>0.2451590244595243</v>
+        <v>0.4960517874846671</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>LC US Equity</t>
+          <t>IOVA US Equity</t>
         </is>
       </c>
       <c r="B31" s="2" t="n">
-        <v>42108</v>
+        <v>43909</v>
       </c>
       <c r="C31" s="2" t="n">
-        <v>42373</v>
+        <v>43983</v>
       </c>
       <c r="D31" t="n">
-        <v>265</v>
+        <v>74</v>
       </c>
       <c r="E31" t="n">
-        <v>0.2484844303043602</v>
+        <v>0.4817989418673881</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>LC US Equity</t>
+          <t>IRDM US Equity</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
-        <v>42389</v>
+        <v>44610</v>
       </c>
       <c r="C32" s="2" t="n">
-        <v>42510</v>
+        <v>45700</v>
       </c>
       <c r="D32" t="n">
-        <v>121</v>
+        <v>1090</v>
       </c>
       <c r="E32" t="n">
-        <v>0.4798186261651735</v>
+        <v>0.2451590244595243</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>MBBYF US Equity</t>
+          <t>LC US Equity</t>
         </is>
       </c>
       <c r="B33" s="2" t="n">
-        <v>42041</v>
+        <v>42108</v>
       </c>
       <c r="C33" s="2" t="n">
-        <v>42312</v>
+        <v>42373</v>
       </c>
       <c r="D33" t="n">
-        <v>271</v>
+        <v>265</v>
       </c>
       <c r="E33" t="n">
-        <v>0.2530496535245101</v>
+        <v>0.2484844303043602</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>MDSO US Equity</t>
+          <t>LC US Equity</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
-        <v>42458</v>
+        <v>42389</v>
       </c>
       <c r="C34" s="2" t="n">
-        <v>42836</v>
+        <v>42510</v>
       </c>
       <c r="D34" t="n">
-        <v>378</v>
+        <v>121</v>
       </c>
       <c r="E34" t="n">
-        <v>0.4980202279847413</v>
+        <v>0.4798186261651735</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>MELI US Equity</t>
+          <t>MBBYF US Equity</t>
         </is>
       </c>
       <c r="B35" s="2" t="n">
-        <v>42402</v>
+        <v>42041</v>
       </c>
       <c r="C35" s="2" t="n">
-        <v>43250</v>
+        <v>42312</v>
       </c>
       <c r="D35" t="n">
-        <v>848</v>
+        <v>271</v>
       </c>
       <c r="E35" t="n">
-        <v>0.5014902113002812</v>
+        <v>0.2530496535245101</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>MELI US Equity</t>
+          <t>MDSO US Equity</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
-        <v>43389</v>
+        <v>42458</v>
       </c>
       <c r="C36" s="2" t="n">
-        <v>43720</v>
+        <v>42836</v>
       </c>
       <c r="D36" t="n">
-        <v>331</v>
+        <v>378</v>
       </c>
       <c r="E36" t="n">
-        <v>0.5042868338863414</v>
+        <v>0.4980202279847413</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>META US Equity</t>
+          <t>MELI US Equity</t>
         </is>
       </c>
       <c r="B37" s="2" t="n">
-        <v>43277</v>
+        <v>42402</v>
       </c>
       <c r="C37" s="2" t="n">
-        <v>43633</v>
+        <v>43250</v>
       </c>
       <c r="D37" t="n">
-        <v>356</v>
+        <v>848</v>
       </c>
       <c r="E37" t="n">
-        <v>1.015456084431241</v>
+        <v>0.5014902113002812</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>META US Equity</t>
+          <t>MELI US Equity</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
-        <v>43690</v>
+        <v>43389</v>
       </c>
       <c r="C38" s="2" t="n">
-        <v>44050</v>
+        <v>43720</v>
       </c>
       <c r="D38" t="n">
-        <v>360</v>
+        <v>331</v>
       </c>
       <c r="E38" t="n">
-        <v>1.128319817305769</v>
+        <v>0.5042868338863414</v>
       </c>
     </row>
     <row r="39">
@@ -1429,662 +1338,662 @@
         </is>
       </c>
       <c r="B39" s="2" t="n">
-        <v>44152</v>
+        <v>43277</v>
       </c>
       <c r="C39" s="2" t="n">
-        <v>45090</v>
+        <v>43633</v>
       </c>
       <c r="D39" t="n">
-        <v>938</v>
+        <v>356</v>
       </c>
       <c r="E39" t="n">
-        <v>0.5117047168118555</v>
+        <v>1.015456084431241</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>NTDOY US Equity</t>
+          <t>META US Equity</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
-        <v>43217</v>
+        <v>43690</v>
       </c>
       <c r="C40" s="2" t="n">
-        <v>44064</v>
+        <v>44050</v>
       </c>
       <c r="D40" t="n">
-        <v>847</v>
+        <v>360</v>
       </c>
       <c r="E40" t="n">
-        <v>0.07378429246598177</v>
+        <v>1.128319817305769</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>NVDA US Equity</t>
+          <t>META US Equity</t>
         </is>
       </c>
       <c r="B41" s="2" t="n">
-        <v>43941</v>
+        <v>44152</v>
       </c>
       <c r="C41" s="2" t="n">
-        <v>44708</v>
+        <v>45090</v>
       </c>
       <c r="D41" t="n">
-        <v>767</v>
+        <v>938</v>
       </c>
       <c r="E41" t="n">
-        <v>0.4049662906836736</v>
+        <v>0.5117047168118555</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>NVDA US Equity</t>
+          <t>NTDOY US Equity</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
-        <v>44937</v>
+        <v>43217</v>
       </c>
       <c r="C42" s="2" t="n">
-        <v>45755</v>
+        <v>44064</v>
       </c>
       <c r="D42" t="n">
-        <v>818</v>
+        <v>847</v>
       </c>
       <c r="E42" t="n">
-        <v>0.3305475183913147</v>
+        <v>0.07378429246598177</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>PACB US Equity</t>
+          <t>NVDA US Equity</t>
         </is>
       </c>
       <c r="B43" s="2" t="n">
-        <v>42065</v>
+        <v>43941</v>
       </c>
       <c r="C43" s="2" t="n">
-        <v>43110</v>
+        <v>44708</v>
       </c>
       <c r="D43" t="n">
-        <v>1045</v>
+        <v>767</v>
       </c>
       <c r="E43" t="n">
-        <v>0.4621782788964639</v>
+        <v>0.4049662906836736</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>PACB US Equity</t>
+          <t>NVDA US Equity</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
-        <v>43427</v>
+        <v>44937</v>
       </c>
       <c r="C44" s="2" t="n">
-        <v>44061</v>
+        <v>45755</v>
       </c>
       <c r="D44" t="n">
-        <v>634</v>
+        <v>818</v>
       </c>
       <c r="E44" t="n">
-        <v>0.003631100790811985</v>
+        <v>0.3305475183913147</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>PINS US Equity</t>
+          <t>PACB US Equity</t>
         </is>
       </c>
       <c r="B45" s="2" t="n">
-        <v>44271</v>
+        <v>42065</v>
       </c>
       <c r="C45" s="2" t="n">
-        <v>45278</v>
+        <v>43110</v>
       </c>
       <c r="D45" t="n">
-        <v>1007</v>
+        <v>1045</v>
       </c>
       <c r="E45" t="n">
-        <v>0.1841894457298311</v>
+        <v>0.4621782788964639</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>PLTR US Equity</t>
+          <t>PACB US Equity</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
-        <v>44620</v>
+        <v>43427</v>
       </c>
       <c r="C46" s="2" t="n">
-        <v>45057</v>
+        <v>44061</v>
       </c>
       <c r="D46" t="n">
-        <v>437</v>
+        <v>634</v>
       </c>
       <c r="E46" t="n">
-        <v>0.5108595090123392</v>
+        <v>0.003631100790811985</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>PRLB US Equity</t>
+          <t>PINS US Equity</t>
         </is>
       </c>
       <c r="B47" s="2" t="n">
-        <v>43277</v>
+        <v>44271</v>
       </c>
       <c r="C47" s="2" t="n">
-        <v>43508</v>
+        <v>45278</v>
       </c>
       <c r="D47" t="n">
-        <v>231</v>
+        <v>1007</v>
       </c>
       <c r="E47" t="n">
-        <v>0.3038956856049196</v>
+        <v>0.1841894457298311</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>PYPL US Equity</t>
+          <t>PLTR US Equity</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
-        <v>43220</v>
+        <v>44620</v>
       </c>
       <c r="C48" s="2" t="n">
-        <v>43861</v>
+        <v>45057</v>
       </c>
       <c r="D48" t="n">
-        <v>641</v>
+        <v>437</v>
       </c>
       <c r="E48" t="n">
-        <v>0.5054318209415705</v>
+        <v>0.5108595090123392</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>PYPL US Equity</t>
+          <t>PRLB US Equity</t>
         </is>
       </c>
       <c r="B49" s="2" t="n">
-        <v>43909</v>
+        <v>43277</v>
       </c>
       <c r="C49" s="2" t="n">
-        <v>44139</v>
+        <v>43508</v>
       </c>
       <c r="D49" t="n">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="E49" t="n">
-        <v>1.011077438029077</v>
+        <v>0.3038956856049196</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>QCOM US Equity</t>
+          <t>PYPL US Equity</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
-        <v>42041</v>
+        <v>43220</v>
       </c>
       <c r="C50" s="2" t="n">
-        <v>42437</v>
+        <v>43861</v>
       </c>
       <c r="D50" t="n">
-        <v>396</v>
+        <v>641</v>
       </c>
       <c r="E50" t="n">
-        <v>0.5063940383503459</v>
+        <v>0.5054318209415705</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>QCOM US Equity</t>
+          <t>PYPL US Equity</t>
         </is>
       </c>
       <c r="B51" s="2" t="n">
-        <v>42492</v>
+        <v>43909</v>
       </c>
       <c r="C51" s="2" t="n">
-        <v>42761</v>
+        <v>44139</v>
       </c>
       <c r="D51" t="n">
-        <v>269</v>
+        <v>230</v>
       </c>
       <c r="E51" t="n">
-        <v>0.9564386412945145</v>
+        <v>1.011077438029077</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>REGN US Equity</t>
+          <t>QCOM US Equity</t>
         </is>
       </c>
       <c r="B52" s="2" t="n">
-        <v>43718</v>
+        <v>42041</v>
       </c>
       <c r="C52" s="2" t="n">
-        <v>44208</v>
+        <v>42437</v>
       </c>
       <c r="D52" t="n">
-        <v>490</v>
+        <v>396</v>
       </c>
       <c r="E52" t="n">
-        <v>0.1485730774152069</v>
+        <v>0.5063940383503459</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>SCHW US Equity</t>
+          <t>QCOM US Equity</t>
         </is>
       </c>
       <c r="B53" s="2" t="n">
-        <v>42004</v>
+        <v>42492</v>
       </c>
       <c r="C53" s="2" t="n">
-        <v>42510</v>
+        <v>42761</v>
       </c>
       <c r="D53" t="n">
-        <v>506</v>
+        <v>269</v>
       </c>
       <c r="E53" t="n">
-        <v>0.5009728625923319</v>
+        <v>0.9564386412945145</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>SE US Equity</t>
+          <t>REGN US Equity</t>
         </is>
       </c>
       <c r="B54" s="2" t="n">
-        <v>43909</v>
+        <v>43718</v>
       </c>
       <c r="C54" s="2" t="n">
-        <v>44062</v>
+        <v>44208</v>
       </c>
       <c r="D54" t="n">
-        <v>153</v>
+        <v>490</v>
       </c>
       <c r="E54" t="n">
-        <v>0.5073047995186792</v>
+        <v>0.1485730774152069</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>SE US Equity</t>
+          <t>SCHW US Equity</t>
         </is>
       </c>
       <c r="B55" s="2" t="n">
-        <v>44487</v>
+        <v>42004</v>
       </c>
       <c r="C55" s="2" t="n">
-        <v>44593</v>
+        <v>42510</v>
       </c>
       <c r="D55" t="n">
-        <v>106</v>
+        <v>506</v>
       </c>
       <c r="E55" t="n">
-        <v>0.02795461985489596</v>
+        <v>0.5009728625923319</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>SNAP US Equity</t>
+          <t>SE US Equity</t>
         </is>
       </c>
       <c r="B56" s="2" t="n">
         <v>43909</v>
       </c>
       <c r="C56" s="2" t="n">
-        <v>44035</v>
+        <v>44062</v>
       </c>
       <c r="D56" t="n">
-        <v>126</v>
+        <v>153</v>
       </c>
       <c r="E56" t="n">
-        <v>0.4945624760246113</v>
+        <v>0.5073047995186792</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>SNAP US Equity</t>
+          <t>SE US Equity</t>
         </is>
       </c>
       <c r="B57" s="2" t="n">
-        <v>44077</v>
+        <v>44487</v>
       </c>
       <c r="C57" s="2" t="n">
-        <v>44235</v>
+        <v>44593</v>
       </c>
       <c r="D57" t="n">
-        <v>158</v>
+        <v>106</v>
       </c>
       <c r="E57" t="n">
-        <v>0.5279001378718579</v>
+        <v>0.02795461985489596</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>SPOT US Equity</t>
+          <t>SNAP US Equity</t>
         </is>
       </c>
       <c r="B58" s="2" t="n">
-        <v>43718</v>
+        <v>43909</v>
       </c>
       <c r="C58" s="2" t="n">
-        <v>43978</v>
+        <v>44035</v>
       </c>
       <c r="D58" t="n">
-        <v>260</v>
+        <v>126</v>
       </c>
       <c r="E58" t="n">
-        <v>0.4853398926368807</v>
+        <v>0.4945624760246113</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>TCEHY US Equity</t>
+          <t>SNAP US Equity</t>
         </is>
       </c>
       <c r="B59" s="2" t="n">
-        <v>43909</v>
+        <v>44077</v>
       </c>
       <c r="C59" s="2" t="n">
-        <v>44076</v>
+        <v>44235</v>
       </c>
       <c r="D59" t="n">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="E59" t="n">
-        <v>0.123539086270048</v>
+        <v>0.5279001378718579</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>TDOC US Equity</t>
+          <t>SPOT US Equity</t>
         </is>
       </c>
       <c r="B60" s="2" t="n">
-        <v>43909</v>
+        <v>43718</v>
       </c>
       <c r="C60" s="2" t="n">
-        <v>44049</v>
+        <v>43978</v>
       </c>
       <c r="D60" t="n">
-        <v>140</v>
+        <v>260</v>
       </c>
       <c r="E60" t="n">
-        <v>0.9832553552772862</v>
+        <v>0.4853398926368807</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>TER US Equity</t>
+          <t>TCEHY US Equity</t>
         </is>
       </c>
       <c r="B61" s="2" t="n">
-        <v>44125</v>
+        <v>43909</v>
       </c>
       <c r="C61" s="2" t="n">
-        <v>44228</v>
+        <v>44076</v>
       </c>
       <c r="D61" t="n">
-        <v>103</v>
+        <v>167</v>
       </c>
       <c r="E61" t="n">
-        <v>0.1473049641047281</v>
+        <v>0.123539086270048</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>TER US Equity</t>
+          <t>TDOC US Equity</t>
         </is>
       </c>
       <c r="B62" s="2" t="n">
-        <v>44474</v>
+        <v>43909</v>
       </c>
       <c r="C62" s="2" t="n">
-        <v>45090</v>
+        <v>44049</v>
       </c>
       <c r="D62" t="n">
-        <v>616</v>
+        <v>140</v>
       </c>
       <c r="E62" t="n">
-        <v>0.03768149071833461</v>
+        <v>0.9832553552772862</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>TREE US Equity</t>
+          <t>TER US Equity</t>
         </is>
       </c>
       <c r="B63" s="2" t="n">
-        <v>43193</v>
+        <v>44125</v>
       </c>
       <c r="C63" s="2" t="n">
-        <v>43312</v>
+        <v>44228</v>
       </c>
       <c r="D63" t="n">
-        <v>119</v>
+        <v>103</v>
       </c>
       <c r="E63" t="n">
-        <v>1.050984313232082</v>
+        <v>0.1473049641047281</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>TRMB US Equity</t>
+          <t>TER US Equity</t>
         </is>
       </c>
       <c r="B64" s="2" t="n">
-        <v>42383</v>
+        <v>44474</v>
       </c>
       <c r="C64" s="2" t="n">
-        <v>44291</v>
+        <v>45090</v>
       </c>
       <c r="D64" t="n">
-        <v>1908</v>
+        <v>616</v>
       </c>
       <c r="E64" t="n">
-        <v>0.1589357122174727</v>
+        <v>0.03768149071833461</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>TSM US Equity</t>
+          <t>TREE US Equity</t>
         </is>
       </c>
       <c r="B65" s="2" t="n">
-        <v>43397</v>
+        <v>43193</v>
       </c>
       <c r="C65" s="2" t="n">
-        <v>44021</v>
+        <v>43312</v>
       </c>
       <c r="D65" t="n">
-        <v>624</v>
+        <v>119</v>
       </c>
       <c r="E65" t="n">
-        <v>0.3591561354308993</v>
+        <v>1.050984313232082</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>TSM US Equity</t>
+          <t>TRMB US Equity</t>
         </is>
       </c>
       <c r="B66" s="2" t="n">
-        <v>44313</v>
+        <v>42383</v>
       </c>
       <c r="C66" s="2" t="n">
-        <v>45797</v>
+        <v>44291</v>
       </c>
       <c r="D66" t="n">
-        <v>1484</v>
+        <v>1908</v>
       </c>
       <c r="E66" t="n">
-        <v>0.4103560491936882</v>
+        <v>0.1589357122174727</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>TTD US Equity</t>
+          <t>TSM US Equity</t>
         </is>
       </c>
       <c r="B67" s="2" t="n">
-        <v>43901</v>
+        <v>43397</v>
       </c>
       <c r="C67" s="2" t="n">
-        <v>45243</v>
+        <v>44021</v>
       </c>
       <c r="D67" t="n">
-        <v>1342</v>
+        <v>624</v>
       </c>
       <c r="E67" t="n">
-        <v>0.5068798618366805</v>
+        <v>0.3591561354308993</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>TWLO US Equity</t>
+          <t>TSM US Equity</t>
         </is>
       </c>
       <c r="B68" s="2" t="n">
-        <v>43040</v>
+        <v>44313</v>
       </c>
       <c r="C68" s="2" t="n">
-        <v>44021</v>
+        <v>45797</v>
       </c>
       <c r="D68" t="n">
-        <v>981</v>
+        <v>1484</v>
       </c>
       <c r="E68" t="n">
-        <v>0.4945969629745466</v>
+        <v>0.4103560491936882</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>TWOUQ US Equity</t>
+          <t>TTD US Equity</t>
         </is>
       </c>
       <c r="B69" s="2" t="n">
-        <v>43217</v>
+        <v>43901</v>
       </c>
       <c r="C69" s="2" t="n">
-        <v>43411</v>
+        <v>45243</v>
       </c>
       <c r="D69" t="n">
-        <v>194</v>
+        <v>1342</v>
       </c>
       <c r="E69" t="n">
-        <v>0.5237886032674073</v>
+        <v>0.5068798618366805</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>TWTR US Equity</t>
+          <t>TWLO US Equity</t>
         </is>
       </c>
       <c r="B70" s="2" t="n">
-        <v>42408</v>
+        <v>43040</v>
       </c>
       <c r="C70" s="2" t="n">
-        <v>42562</v>
+        <v>44021</v>
       </c>
       <c r="D70" t="n">
-        <v>154</v>
+        <v>981</v>
       </c>
       <c r="E70" t="n">
-        <v>0.4892660769048036</v>
+        <v>0.4945969629745466</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>TWTR US Equity</t>
+          <t>TWOUQ US Equity</t>
         </is>
       </c>
       <c r="B71" s="2" t="n">
-        <v>43927</v>
+        <v>43217</v>
       </c>
       <c r="C71" s="2" t="n">
-        <v>44250</v>
+        <v>43411</v>
       </c>
       <c r="D71" t="n">
-        <v>323</v>
+        <v>194</v>
       </c>
       <c r="E71" t="n">
-        <v>0.276087329749161</v>
+        <v>0.5237886032674073</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>USD Curncy</t>
+          <t>TWTR US Equity</t>
         </is>
       </c>
       <c r="B72" s="2" t="n">
-        <v>42004</v>
+        <v>42408</v>
       </c>
       <c r="C72" s="2" t="n">
-        <v>42041</v>
+        <v>42562</v>
       </c>
       <c r="D72" t="n">
-        <v>37</v>
+        <v>154</v>
       </c>
       <c r="E72" t="n">
-        <v>0</v>
+        <v>0.4892660769048036</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>XLNX US Equity</t>
+          <t>TWTR US Equity</t>
         </is>
       </c>
       <c r="B73" s="2" t="n">
-        <v>42397</v>
+        <v>43927</v>
       </c>
       <c r="C73" s="2" t="n">
-        <v>42766</v>
+        <v>44250</v>
       </c>
       <c r="D73" t="n">
-        <v>369</v>
+        <v>323</v>
       </c>
       <c r="E73" t="n">
-        <v>0.9656078142539634</v>
+        <v>0.276087329749161</v>
       </c>
     </row>
     <row r="74">
@@ -2094,34 +2003,53 @@
         </is>
       </c>
       <c r="B74" s="2" t="n">
-        <v>43389</v>
+        <v>42397</v>
       </c>
       <c r="C74" s="2" t="n">
-        <v>43581</v>
+        <v>42766</v>
       </c>
       <c r="D74" t="n">
-        <v>192</v>
+        <v>369</v>
       </c>
       <c r="E74" t="n">
-        <v>0.4992442592796971</v>
+        <v>0.9656078142539634</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
+          <t>XLNX US Equity</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="n">
+        <v>43389</v>
+      </c>
+      <c r="C75" s="2" t="n">
+        <v>43581</v>
+      </c>
+      <c r="D75" t="n">
+        <v>192</v>
+      </c>
+      <c r="E75" t="n">
+        <v>0.4992442592796971</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
           <t>Z US Equity</t>
         </is>
       </c>
-      <c r="B75" s="2" t="n">
+      <c r="B76" s="2" t="n">
         <v>42375</v>
       </c>
-      <c r="C75" s="2" t="n">
+      <c r="C76" s="2" t="n">
         <v>43320</v>
       </c>
-      <c r="D75" t="n">
+      <c r="D76" t="n">
         <v>945</v>
       </c>
-      <c r="E75" t="n">
+      <c r="E76" t="n">
         <v>1.22404643619271</v>
       </c>
     </row>
